--- a/quizzes/029_digestive_disorders_quiz--quizzes.xlsx
+++ b/quizzes/029_digestive_disorders_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_"crohn's_disease"}</t>
+          <t>crohn's_disease</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': "Crohn's disease"}</t>
+          <t>Crohn's disease</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'ulcerative_colitis'}</t>
+          <t>ulcerative_colitis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Ulcerative colitis'}</t>
+          <t>Ulcerative colitis</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'celiac_disease'}</t>
+          <t>celiac_disease</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Celiac disease'}</t>
+          <t>Celiac disease</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'irritable_bowel_syndrome_(ibs)'}</t>
+          <t>irritable_bowel_syndrome_(ibs)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Irritable bowel syndrome (IBS)'}</t>
+          <t>Irritable bowel syndrome (IBS)</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'nausea_and_vomiting'}</t>
+          <t>nausea_and_vomiting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Nausea and vomiting'}</t>
+          <t>Nausea and vomiting</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'abdominal_pain'}</t>
+          <t>abdominal_pain</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Abdominal pain'}</t>
+          <t>Abdominal pain</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'blood_in_stool'}</t>
+          <t>blood_in_stool</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Blood in stool'}</t>
+          <t>Blood in stool</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'diarrhea'}</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Diarrhea'}</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'abdominal_distension'}</t>
+          <t>abdominal_distension</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Abdominal distension'}</t>
+          <t>Abdominal distension</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'weight_loss'}</t>
+          <t>weight_loss</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Weight loss'}</t>
+          <t>Weight loss</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'other_symptoms'}</t>
+          <t>other_symptoms</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Other symptoms'}</t>
+          <t>Other symptoms</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'option4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'option4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'option5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'option5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'option4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'option4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'option5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'option5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'option4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'option4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'option5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'option5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'option4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'option4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'option5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'option5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'option2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'option2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'option3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'option3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'option4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'option4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'option5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'option5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
